--- a/每日输出/初短一部/郑州-初短一部-风灵个微全天在线率&爱芯后台授权.xlsx
+++ b/每日输出/初短一部/郑州-初短一部-风灵个微全天在线率&爱芯后台授权.xlsx
@@ -181,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -207,16 +207,10 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1492,86 +1486,86 @@
         <v>7</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9" t="e">
-        <v>#N/A</v>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>初三 汇总</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n">
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="10" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="12" t="e">
-        <v>#N/A</v>
+      <c r="H4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>初中</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>初中 汇总</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="10" t="n">
+      <c r="C5" s="9" t="inlineStr"/>
+      <c r="D5" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="12" t="e">
-        <v>#N/A</v>
+      <c r="H5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1617,14 +1611,421 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>无数据</t>
-        </is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>学部</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>年级</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>战队</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>老师邮箱</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>老师姓名</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>个微授权</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>整体正常</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>运营中心</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>小时</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>fuyang</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>付洋</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>liguo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>李果</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>linsai</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>林赛</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lishujuan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>李淑娟</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>liyiteng</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>李一腾</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>songkaida</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>宋开达</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>初短一部</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>青云逐峰</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>wangendian</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>王恩点</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>郑州一部</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1703,13 +2104,16 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
